--- a/artfynd/A 19200-2025 artfynd.xlsx
+++ b/artfynd/A 19200-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1602,6 +1602,782 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128900642</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91800</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>658</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sörgraninge, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>609868</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6983542</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128900637</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79120</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sörgraninge, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>609846</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6983596</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128900644</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91454</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>112</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stjärntagging</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Asterodon ferruginosus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pat.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sörgraninge, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>609854</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6983509</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128900643</v>
+      </c>
+      <c r="B12" t="n">
+        <v>75205</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sörgraninge, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>609860</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6983546</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128900639</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91911</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sörgraninge, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>609884</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6983579</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128900641</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sörgraninge, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>609880</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6983537</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128900631</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91504</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sörgraninge, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>609902</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6983513</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128900633</v>
+      </c>
+      <c r="B16" t="n">
+        <v>75205</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sörgraninge, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>609761</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6983545</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Graninge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Clara Lerbro</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19200-2025 artfynd.xlsx
+++ b/artfynd/A 19200-2025 artfynd.xlsx
@@ -1605,10 +1605,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900642</v>
+        <v>128900637</v>
       </c>
       <c r="B9" t="n">
-        <v>91800</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,21 +1616,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609868</v>
+        <v>609846</v>
       </c>
       <c r="R9" t="n">
-        <v>6983542</v>
+        <v>6983596</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900637</v>
+        <v>128900642</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>91800</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,21 +1713,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609846</v>
+        <v>609868</v>
       </c>
       <c r="R10" t="n">
-        <v>6983596</v>
+        <v>6983542</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>

--- a/artfynd/A 19200-2025 artfynd.xlsx
+++ b/artfynd/A 19200-2025 artfynd.xlsx
@@ -1799,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900644</v>
+        <v>128900643</v>
       </c>
       <c r="B11" t="n">
-        <v>91454</v>
+        <v>75205</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,37 +1810,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörgraninge, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609854</v>
+        <v>609860</v>
       </c>
       <c r="R11" t="n">
-        <v>6983509</v>
+        <v>6983546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1881,7 +1878,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900643</v>
+        <v>128900644</v>
       </c>
       <c r="B12" t="n">
-        <v>75205</v>
+        <v>91454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,34 +1907,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörgraninge, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609860</v>
+        <v>609854</v>
       </c>
       <c r="R12" t="n">
-        <v>6983546</v>
+        <v>6983509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,6 +1978,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 19200-2025 artfynd.xlsx
+++ b/artfynd/A 19200-2025 artfynd.xlsx
@@ -1605,10 +1605,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128900637</v>
+        <v>128900642</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>91804</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,21 +1616,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1640,10 +1640,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609846</v>
+        <v>609868</v>
       </c>
       <c r="R9" t="n">
-        <v>6983596</v>
+        <v>6983542</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1702,10 +1702,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128900642</v>
+        <v>128900637</v>
       </c>
       <c r="B10" t="n">
-        <v>91800</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1713,21 +1713,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609868</v>
+        <v>609846</v>
       </c>
       <c r="R10" t="n">
-        <v>6983542</v>
+        <v>6983596</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900643</v>
+        <v>128900644</v>
       </c>
       <c r="B11" t="n">
-        <v>75205</v>
+        <v>91458</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,34 +1810,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörgraninge, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609860</v>
+        <v>609854</v>
       </c>
       <c r="R11" t="n">
-        <v>6983546</v>
+        <v>6983509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,6 +1881,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1896,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900644</v>
+        <v>128900643</v>
       </c>
       <c r="B12" t="n">
-        <v>91454</v>
+        <v>75209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,37 +1911,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörgraninge, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609854</v>
+        <v>609860</v>
       </c>
       <c r="R12" t="n">
-        <v>6983509</v>
+        <v>6983546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1979,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1997,27 +1997,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900639</v>
+        <v>128900641</v>
       </c>
       <c r="B13" t="n">
-        <v>91911</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2027,10 +2032,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609884</v>
+        <v>609880</v>
       </c>
       <c r="R13" t="n">
-        <v>6983579</v>
+        <v>6983537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,7 +2076,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2090,32 +2094,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900641</v>
+        <v>128900639</v>
       </c>
       <c r="B14" t="n">
-        <v>98632</v>
+        <v>91915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609880</v>
+        <v>609884</v>
       </c>
       <c r="R14" t="n">
-        <v>6983537</v>
+        <v>6983579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,6 +2168,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>128900631</v>
       </c>
       <c r="B15" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>128900633</v>
       </c>
       <c r="B16" t="n">
-        <v>75205</v>
+        <v>75209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 19200-2025 artfynd.xlsx
+++ b/artfynd/A 19200-2025 artfynd.xlsx
@@ -1799,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900644</v>
+        <v>128900643</v>
       </c>
       <c r="B11" t="n">
-        <v>91458</v>
+        <v>75209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,37 +1810,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörgraninge, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609854</v>
+        <v>609860</v>
       </c>
       <c r="R11" t="n">
-        <v>6983509</v>
+        <v>6983546</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1881,7 +1878,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1896,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900643</v>
+        <v>128900644</v>
       </c>
       <c r="B12" t="n">
-        <v>75209</v>
+        <v>91458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1911,34 +1907,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörgraninge, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609860</v>
+        <v>609854</v>
       </c>
       <c r="R12" t="n">
-        <v>6983546</v>
+        <v>6983509</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,6 +1978,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 19200-2025 artfynd.xlsx
+++ b/artfynd/A 19200-2025 artfynd.xlsx
@@ -1997,32 +1997,27 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900641</v>
+        <v>128900639</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>91915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2032,10 +2027,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609880</v>
+        <v>609884</v>
       </c>
       <c r="R13" t="n">
-        <v>6983537</v>
+        <v>6983579</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2076,6 +2071,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2094,27 +2090,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900639</v>
+        <v>128900641</v>
       </c>
       <c r="B14" t="n">
-        <v>91915</v>
+        <v>98636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2124,10 +2125,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609884</v>
+        <v>609880</v>
       </c>
       <c r="R14" t="n">
-        <v>6983579</v>
+        <v>6983537</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2169,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 19200-2025 artfynd.xlsx
+++ b/artfynd/A 19200-2025 artfynd.xlsx
@@ -1608,7 +1608,7 @@
         <v>128900642</v>
       </c>
       <c r="B9" t="n">
-        <v>91804</v>
+        <v>91809</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1705,7 +1705,7 @@
         <v>128900637</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1799,10 +1799,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128900643</v>
+        <v>128900644</v>
       </c>
       <c r="B11" t="n">
-        <v>75209</v>
+        <v>91463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,34 +1810,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Sörgraninge, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609860</v>
+        <v>609854</v>
       </c>
       <c r="R11" t="n">
-        <v>6983546</v>
+        <v>6983509</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1878,6 +1881,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1896,10 +1900,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128900644</v>
+        <v>128900643</v>
       </c>
       <c r="B12" t="n">
-        <v>91458</v>
+        <v>83005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,37 +1911,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>112</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Sörgraninge, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609854</v>
+        <v>609860</v>
       </c>
       <c r="R12" t="n">
-        <v>6983509</v>
+        <v>6983546</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1978,7 +1979,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1997,27 +1997,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128900639</v>
+        <v>128900641</v>
       </c>
       <c r="B13" t="n">
-        <v>91915</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6040186</v>
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2027,10 +2032,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609884</v>
+        <v>609880</v>
       </c>
       <c r="R13" t="n">
-        <v>6983579</v>
+        <v>6983537</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,7 +2076,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2090,32 +2094,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128900641</v>
+        <v>128900639</v>
       </c>
       <c r="B14" t="n">
-        <v>98636</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2125,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609880</v>
+        <v>609884</v>
       </c>
       <c r="R14" t="n">
-        <v>6983537</v>
+        <v>6983579</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2169,6 +2168,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>128900631</v>
       </c>
       <c r="B15" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2287,7 +2287,7 @@
         <v>128900633</v>
       </c>
       <c r="B16" t="n">
-        <v>75209</v>
+        <v>83005</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
